--- a/legal_forms/010_greenhouse_management_agreement--legal_forms.xlsx
+++ b/legal_forms/010_greenhouse_management_agreement--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>greenhouse_owner</t>
+          <t>greenhouse_owner_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Greenhouse Owner</t>
+          <t>Greenhouse Owner Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +543,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>owner_name</t>
+          <t>greenhouse_location</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>owner_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Greenhouse Location</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please specify the location of the greenhouse.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,58 +570,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>greenhouse_location</t>
+          <t>agreement_dates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greenhouse Location</t>
+          <t>Agreement Dates</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>payment_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Payment Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rent_amount</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rent_amount</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,92 +657,92 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>agreement_end_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>Agreement End Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>payment_frequency</t>
+          <t>rent_amount</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>payment_frequency</t>
+          <t>Rent Amount</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>payment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>payment_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Payment Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>total_rent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Total Rent</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +772,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_phone2</t>
+          <t>notes2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Notes2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +795,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>agreement_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Agreement Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +818,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>signature2</t>
+          <t>agreement_end_date2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>signature2</t>
+          <t>Agreement End Date2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +841,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>agreement_date</t>
+          <t>notes3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>agreement_date</t>
+          <t>More Additional Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,46 +864,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>agreement_end_date</t>
+          <t>payment2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>agreement_end_date</t>
+          <t>Payment2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>greenhouse_id</t>
+          <t>payment_frequency2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>greenhouse_id</t>
+          <t>Payment Frequency2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +915,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>total_rent</t>
+          <t>total_rent2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>total_rent</t>
+          <t>Total Rent2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>payment_method2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>payment_frequency2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>payment_frequency</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>notes2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>notes2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_email2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_phone3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact_phone3</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>signature3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>signature3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>signature4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>signature4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +945,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +969,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1042,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1216,63 +1059,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payment_choices</t>
+          <t>payment2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>payment_choices</t>
+          <t>payment2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>payment_choices</t>
+          <t>payment2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1127,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_1}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 1}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1144,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_2}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 2}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1161,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_3}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 3}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
